--- a/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.06%2375</t>
+          <t>+1.47%2410</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2375</v>
+        <v>2410</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-3.77%3700</t>
+          <t>+2.43%3790</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3700</v>
+        <v>3790</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.78%6325</t>
+          <t>-1.11%6255</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6325</v>
+        <v>6255</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0%766</t>
+          <t>-0.52%762</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.21%13925</t>
+          <t>-3.88%13385</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>13925</v>
+        <v>13385</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.79%5985</t>
+          <t>-5.1%5680</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5985</v>
+        <v>5680</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+4.26%379</t>
+          <t>-1.58%373</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+4.26%</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.94%2140</t>
+          <t>-1.87%2100</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2140</v>
+        <v>2100</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+7.52%5650</t>
+          <t>-3.27%5465</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+7.52%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5650</v>
+        <v>5465</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.94%2105</t>
+          <t>-3.33%2035</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2105</v>
+        <v>2035</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.31%463</t>
+          <t>-4.75%441</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.63%5515</t>
+          <t>+1.72%5610</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5515</v>
+        <v>5610</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+4.9%1285</t>
+          <t>-0.39%1280</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+4.9%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+5.38%882</t>
+          <t>+0.11%883</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+5.38%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:45</t>
+          <t>2026-08-21 14:42:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.55%2985</t>
+          <t>-4.02%2865</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.55%</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2985</v>
+        <v>2865</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.02%993</t>
+          <t>-5.24%941</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-5.24%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>993</v>
+        <v>941</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.97%208.5</t>
+          <t>-2.64%203</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>208.5</v>
+        <v>203</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.99%713</t>
+          <t>-1.26%704</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+5%1575</t>
+          <t>-5.08%1495</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+5%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1575</v>
+        <v>1495</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+5.67%186.5</t>
+          <t>-5.63%176</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+5.67%</t>
+          <t>-5.63%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>186.5</v>
+        <v>176</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+3.91%412</t>
+          <t>-1.46%406</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+3.91%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.84%180</t>
+          <t>-0.28%179.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>180</v>
+        <v>179.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+4.09%267</t>
+          <t>-5.06%253.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+4.09%</t>
+          <t>-5.06%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>267</v>
+        <v>253.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.29%344</t>
+          <t>-1.31%339.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>344</v>
+        <v>339.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.1%180</t>
+          <t>-2.5%175.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>180</v>
+        <v>175.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0%140</t>
+          <t>+1.07%141.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>140</v>
+        <v>141.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.38%267</t>
+          <t>-2.25%261</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0%115.5</t>
+          <t>+0.87%116.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>115.5</v>
+        <v>116.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-3.03%673</t>
+          <t>-3.57%649</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>673</v>
+        <v>649</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:47</t>
+          <t>2026-08-21 14:42:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-3.32%174.5</t>
+          <t>-4.01%167.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-3.32%</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>174.5</v>
+        <v>167.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.1%172</t>
+          <t>-4.07%165</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-4.07%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.46%128.5</t>
+          <t>-3.89%123.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.46%</t>
+          <t>-3.89%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>128.5</v>
+        <v>123.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.34%590</t>
+          <t>-0.51%587</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.51%15750</t>
+          <t>-2.54%15350</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>15750</v>
+        <v>15350</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+2.38%560</t>
+          <t>0%560</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+2.38%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>-3.96%1090</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.96%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1135</v>
+        <v>1090</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.57%878</t>
+          <t>+0.23%880</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.57%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.21%2210</t>
+          <t>-2.49%2155</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2210</v>
+        <v>2155</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.29%268.5</t>
+          <t>-0.37%267.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>268.5</v>
+        <v>267.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+5.37%510</t>
+          <t>+0.59%513</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+5.37%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.23%287.5</t>
+          <t>-6.96%267.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-6.96%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>287.5</v>
+        <v>267.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.42%119.5</t>
+          <t>-2.51%116.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-2.51%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>119.5</v>
+        <v>116.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.8%496</t>
+          <t>-1.11%490.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>496</v>
+        <v>490.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.17%254</t>
+          <t>+2.17%259.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>254</v>
+        <v>259.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:48</t>
+          <t>2026-08-21 14:42:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.57%50.2</t>
+          <t>-2.79%48.8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.57%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>50.2</v>
+        <v>48.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.63%90.3</t>
+          <t>-2.33%88.2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>90.3</v>
+        <v>88.2</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.64%62.1</t>
+          <t>+3.06%64</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+3.06%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>62.1</v>
+        <v>64</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+10%445.5</t>
+          <t>+2.13%455</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>445.5</v>
+        <v>455</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.79%1375</t>
+          <t>+1.82%1400</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0%47.05</t>
+          <t>+0.96%47.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>47.05</v>
+        <v>47.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+6.33%5630</t>
+          <t>-0.53%5600</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+6.33%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>5630</v>
+        <v>5600</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>+1.27%1195</t>
+          <t>-5.02%1135</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1195</v>
+        <v>1135</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0%184</t>
+          <t>-1.09%182</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>+1.25%727</t>
+          <t>-0.55%723</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>+1.25%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3803,16 +3803,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+0.73%413.5</t>
+          <t>+5.44%436</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>413.5</v>
+        <v>436</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-0.66%90.1</t>
+          <t>-0.11%90</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3925,16 +3925,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-1.38%46.4</t>
+          <t>+1.19%46.95</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+1.19%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>46.4</v>
+        <v>46.95</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:49</t>
+          <t>2026-08-21 14:42:24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3986,16 +3986,16 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-0.39%128</t>
+          <t>+4.69%134</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:20</t>
+          <t>2026-08-21 14:54:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:21</t>
+          <t>2026-08-21 14:54:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:23</t>
+          <t>2026-08-21 14:54:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:24</t>
+          <t>2026-08-21 14:54:50</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">

--- a/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">

--- a/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">

--- a/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">

--- a/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00982A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.61%1,794,000</t>
+          <t>8.87%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.61%</t>
+          <t>8.87%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.52%872,000</t>
+          <t>6.78%872,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.52%</t>
+          <t>6.78%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.52%510,000</t>
+          <t>6.54%510,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.52%</t>
+          <t>6.54%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.92%3,828,000</t>
+          <t>5.98%3,828,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>5.98%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.20%185,000</t>
+          <t>5.08%185,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.20%</t>
+          <t>5.08%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.87%320,000</t>
+          <t>3.73%320,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.65%844,000</t>
+          <t>3.63%844,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.50%307,000</t>
+          <t>3.44%307,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.47%817,000</t>
+          <t>3.41%817,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.41%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.75%441</t>
+          <t>+0.11%883</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>441</v>
+        <v>883</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.97%3,178,000</t>
+          <t>2.99%1,650,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3178000</v>
+        <v>1650000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.86%257,000</t>
+          <t>2.96%257,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.39%1280</t>
+          <t>-4.75%441</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1280</v>
+        <v>441</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.60%1,000,000</t>
+          <t>2.87%3,178,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1000000</v>
+        <v>3178000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.11%883</t>
+          <t>-0.39%1280</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>883</v>
+        <v>1280</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.57%1,440,000</t>
+          <t>2.62%1,000,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1440000</v>
+        <v>1000000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:55</t>
+          <t>2026-08-21 17:28:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.29%379,000</t>
+          <t>2.23%379,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.24%1,117,000</t>
+          <t>2.16%1,117,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.64%203</t>
+          <t>-1.26%704</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>203</v>
+        <v>704</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.01%4,780,000</t>
+          <t>1.67%1,158,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>4780000</v>
+        <v>1158000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.26%704</t>
+          <t>-2.64%203</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.26%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>704</v>
+        <v>203</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.67%1,158,000</t>
+          <t>1.66%3,985,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1158000</v>
+        <v>3985000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.38%434,000</t>
+          <t>1.33%434,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-5.63%176</t>
+          <t>-1.46%406</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.63%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>176</v>
+        <v>406</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.33%3,533,000</t>
+          <t>1.31%1,572,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3533000</v>
+        <v>1572000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.46%406</t>
+          <t>-0.28%179.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>406</v>
+        <v>179.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.31%1,572,000</t>
+          <t>1.29%3,504,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1572000</v>
+        <v>3504000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,25 +1785,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.28%179.5</t>
+          <t>-5.63%176</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-5.63%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>179.5</v>
+        <v>176</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.27%3,504,000</t>
+          <t>1.27%3,533,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3504000</v>
+        <v>3533000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,25 +1846,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2428興勤</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.06%253.5</t>
+          <t>+1.07%141.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.06%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>253.5</v>
+        <v>141.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.27%2,356,000</t>
+          <t>1.27%4,386,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1873,11 +1873,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2356000</v>
+        <v>4386000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.31%339.5</t>
+          <t>+0.87%116.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>339.5</v>
+        <v>116.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.25%1,800,000</t>
+          <t>1.26%5,285,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1800000</v>
+        <v>5285000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,25 +1968,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.5%175.5</t>
+          <t>-1.31%339.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>175.5</v>
+        <v>339.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.25%3,432,000</t>
+          <t>1.25%1,800,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1995,11 +1995,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3432000</v>
+        <v>1800000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,25 +2029,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.07%141.5</t>
+          <t>-2.5%175.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>141.5</v>
+        <v>175.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.24%4,386,000</t>
+          <t>1.24%3,432,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2056,11 +2056,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>4386000</v>
+        <v>3432000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2428興勤</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.87%116.5</t>
+          <t>-5.06%253.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-5.06%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>116.5</v>
+        <v>253.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.23%5,285,000</t>
+          <t>1.22%2,356,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>5285000</v>
+        <v>2356000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.22%901,000</t>
+          <t>1.20%901,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:56</t>
+          <t>2026-08-21 17:28:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.22%3,472,000</t>
+          <t>1.19%3,472,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-4.07%165</t>
+          <t>-0.51%587</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-4.07%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>165</v>
+        <v>587</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.18%3,396,000</t>
+          <t>1.15%959,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>3396000</v>
+        <v>959000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2478大毅</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.89%123.5</t>
+          <t>-4.07%165</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.89%</t>
+          <t>-4.07%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>123.5</v>
+        <v>165</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.16%4,484,000</t>
+          <t>1.15%3,396,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>4484000</v>
+        <v>3396000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.51%587</t>
+          <t>0%560</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>587</v>
+        <v>560</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.14%959,000</t>
+          <t>1.15%1,000,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>959000</v>
+        <v>1000000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2478大毅</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.54%15350</t>
+          <t>-3.89%123.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.54%</t>
+          <t>-3.89%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>15350</v>
+        <v>123.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.14%35,900</t>
+          <t>1.14%4,484,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>35900</v>
+        <v>4484000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0%560</t>
+          <t>-2.54%15350</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>560</v>
+        <v>15350</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.13%1,000,000</t>
+          <t>1.13%35,900</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,11 +2605,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1000000</v>
+        <v>35900</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.88%382,000</t>
+          <t>0.85%382,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.81%459,000</t>
+          <t>0.83%459,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>6472保瑞</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.49%2155</t>
+          <t>+2.13%455</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2155</v>
+        <v>455</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.42%93,000</t>
+          <t>0.48%516,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>93000</v>
+        <v>516000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>2486一詮</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.37%267.5</t>
+          <t>-2.99%243.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>267.5</v>
+        <v>243.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.39%710,000</t>
+          <t>0.47%950,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>710000</v>
+        <v>950000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.59%513</t>
+          <t>-2.49%2155</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>513</v>
+        <v>2155</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.33%321,000</t>
+          <t>0.41%93,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>321000</v>
+        <v>93000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6672騰輝電子-KY</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-6.96%267.5</t>
+          <t>-0.37%267.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6.96%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2962,20 +2962,20 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.32%546,000</t>
+          <t>0.39%710,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>546000</v>
+        <v>710000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2476鉅祥</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-2.51%116.5</t>
+          <t>+0.59%513</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-2.51%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>116.5</v>
+        <v>513</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.31%1,303,000</t>
+          <t>0.34%321,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1303000</v>
+        <v>321000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>3617碩天</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.11%490.5</t>
+          <t>+2.17%259.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>490.5</v>
+        <v>259.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.31%310,000</t>
+          <t>0.32%603,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>310000</v>
+        <v>603000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3617碩天</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2.17%259.5</t>
+          <t>-1.11%490.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>259.5</v>
+        <v>490.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.31%603,000</t>
+          <t>0.31%310,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>603000</v>
+        <v>310000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:57</t>
+          <t>2026-08-21 17:28:03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,34 +3188,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8070長華*</t>
+          <t>2476鉅祥</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.79%48.8</t>
+          <t>-2.51%116.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>-2.51%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>48.8</v>
+        <v>116.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.29%2,871,000</t>
+          <t>0.31%1,303,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>2871000</v>
+        <v>1303000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>6672騰輝電子-KY</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-2.33%88.2</t>
+          <t>-6.96%267.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>-6.96%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>88.2</v>
+        <v>267.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.28%1,544,000</t>
+          <t>0.30%546,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1544000</v>
+        <v>546000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.28%2,213,556</t>
+          <t>0.29%2,213,556</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6472保瑞</t>
+          <t>8070長華*</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+2.13%455</t>
+          <t>-2.79%48.8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>455</v>
+        <v>48.8</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.23%258,000</t>
+          <t>0.29%2,871,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>258000</v>
+        <v>2871000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.82%1400</t>
+          <t>-2.33%88.2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1400</v>
+        <v>88.2</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.12%42,000</t>
+          <t>0.28%1,544,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>42000</v>
+        <v>1544000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,34 +3493,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6177達麗</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.96%47.5</t>
+          <t>+1.82%1400</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>47.5</v>
+        <v>1400</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.02%194,350</t>
+          <t>0.12%42,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>194350</v>
+        <v>42000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3554,38 +3554,38 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>6177達麗</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-0.53%5600</t>
+          <t>+0.96%47.5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>5600</v>
+        <v>47.5</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>0.02%194,350</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>1000</v>
+        <v>194350</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3615,30 +3615,30 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-5.02%1135</t>
+          <t>-0.53%5600</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-5.02%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1135</v>
+        <v>5600</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3676,25 +3676,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4441振大環球</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-1.09%182</t>
+          <t>-5.02%1135</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>182</v>
+        <v>1135</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>&lt;0.01%4,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3737,25 +3737,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1519華城</t>
+          <t>4441振大環球</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-0.55%723</t>
+          <t>-1.09%182</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>723</v>
+        <v>182</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>&lt;0.01%660</t>
+          <t>&lt;0.01%4,000</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>660</v>
+        <v>4000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3798,25 +3798,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>1519華城</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+5.44%436</t>
+          <t>-0.55%723</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>436</v>
+        <v>723</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%660</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3825,11 +3825,11 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3859,25 +3859,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3706神達</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-0.11%90</t>
+          <t>+5.44%436</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>90</v>
+        <v>436</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,400</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3886,11 +3886,11 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3920,38 +3920,38 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2886兆豐金</t>
+          <t>3706神達</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>+1.19%46.95</t>
+          <t>-0.11%90</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>46.95</v>
+        <v>90</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%1,400</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:59</t>
+          <t>2026-08-21 17:28:05</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3981,41 +3981,102 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>2886兆豐金</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>+1.19%46.95</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>+1.19%</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>46.95</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-08-21 17:28:05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>2881富邦金</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>+4.69%134</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>+4.69%</t>
         </is>
       </c>
-      <c r="H59" t="n">
+      <c r="H60" t="n">
         <v>134</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>0%250</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K59" t="n">
+      <c r="K60" t="n">
         <v>250</v>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
